--- a/Lab03 - Data Acquisition/notebooks/task2_deliverables/task3_results.xlsx
+++ b/Lab03 - Data Acquisition/notebooks/task2_deliverables/task3_results.xlsx
@@ -79,22 +79,22 @@
     <t>2014-02-25T08:00:08Z</t>
   </si>
   <si>
-    <t>2026-03-02T12:43:15Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T12:26:45Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T12:00:55Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T09:05:10Z</t>
-  </si>
-  <si>
-    <t>2026-03-02T06:32:43Z</t>
-  </si>
-  <si>
-    <t>Exported at: 2026-03-02 14:50:04.238151</t>
+    <t>2026-03-05T22:34:46Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T22:36:30Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T21:44:37Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T17:52:10Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T21:23:08Z</t>
+  </si>
+  <si>
+    <t>Exported at: 2026-03-06 00:44:54.386230</t>
   </si>
 </sst>
 </file>
@@ -479,16 +479,16 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>193960</v>
+        <v>194010</v>
       </c>
       <c r="C2">
-        <v>75215</v>
+        <v>75217</v>
       </c>
       <c r="D2">
-        <v>3594</v>
+        <v>3599</v>
       </c>
       <c r="E2">
-        <v>193960</v>
+        <v>194010</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
@@ -505,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>97880</v>
+        <v>97984</v>
       </c>
       <c r="C3">
-        <v>27034</v>
+        <v>27081</v>
       </c>
       <c r="D3">
-        <v>18060</v>
+        <v>18086</v>
       </c>
       <c r="E3">
-        <v>97880</v>
+        <v>97984</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
@@ -531,16 +531,16 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>65267</v>
+        <v>65297</v>
       </c>
       <c r="C4">
-        <v>26737</v>
+        <v>26751</v>
       </c>
       <c r="D4">
-        <v>2147</v>
+        <v>2136</v>
       </c>
       <c r="E4">
-        <v>65267</v>
+        <v>65297</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
@@ -557,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>63887</v>
+        <v>63911</v>
       </c>
       <c r="C5">
-        <v>19713</v>
+        <v>19714</v>
       </c>
       <c r="D5">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E5">
-        <v>63887</v>
+        <v>63911</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -583,16 +583,16 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>42909</v>
+        <v>42931</v>
       </c>
       <c r="C6">
-        <v>29083</v>
+        <v>29089</v>
       </c>
       <c r="D6">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E6">
-        <v>42909</v>
+        <v>42931</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>

--- a/Lab03 - Data Acquisition/notebooks/task2_deliverables/task3_results.xlsx
+++ b/Lab03 - Data Acquisition/notebooks/task2_deliverables/task3_results.xlsx
@@ -7,14 +7,16 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Search Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Trending Repos" sheetId="2" r:id="rId2"/>
+    <sheet name="Repository Comparison" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="178">
   <si>
     <t>name</t>
   </si>
@@ -25,21 +27,480 @@
     <t>forks</t>
   </si>
   <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>donnemartin/data-science-ipython-notebooks</t>
+  </si>
+  <si>
+    <t>kedro-org/kedro</t>
+  </si>
+  <si>
+    <t>OpenMined/PySyft</t>
+  </si>
+  <si>
+    <t>drivendataorg/cookiecutter-data-science</t>
+  </si>
+  <si>
+    <t>joelgrus/data-science-from-scratch</t>
+  </si>
+  <si>
+    <t>krishnaik06/The-Grand-Complete-Data-Science-Materials</t>
+  </si>
+  <si>
+    <t>rushter/data-science-blogs</t>
+  </si>
+  <si>
+    <t>ujjwalkarn/DataSciencePython</t>
+  </si>
+  <si>
+    <t>business-science/ai-data-science-team</t>
+  </si>
+  <si>
+    <t>ruc-datalab/DeepAnalyze</t>
+  </si>
+  <si>
+    <t>google/deepvariant</t>
+  </si>
+  <si>
+    <t>colour-science/colour</t>
+  </si>
+  <si>
+    <t>NannyML/nannyml</t>
+  </si>
+  <si>
+    <t>galaxyproject/galaxy</t>
+  </si>
+  <si>
+    <t>fossasia/pslab-expeyes</t>
+  </si>
+  <si>
+    <t>DLLXW/data-science-competition</t>
+  </si>
+  <si>
+    <t>d6t/d6tflow</t>
+  </si>
+  <si>
+    <t>AmoDinho/datacamp-python-data-science-track</t>
+  </si>
+  <si>
+    <t>googleapis/python-aiplatform</t>
+  </si>
+  <si>
+    <t>CodeCutTech/data-science-template</t>
+  </si>
+  <si>
+    <t>tajpouria/algorithms-and-data-structures-cheat-sheet</t>
+  </si>
+  <si>
+    <t>Scifabric/pybossa</t>
+  </si>
+  <si>
+    <t>jeongyoonlee/Kaggler</t>
+  </si>
+  <si>
+    <t>lupantech/ScienceQA</t>
+  </si>
+  <si>
+    <t>SciTools/iris</t>
+  </si>
+  <si>
+    <t>litaotao/IPython-Dashboard</t>
+  </si>
+  <si>
+    <t>rnorm/book_sample</t>
+  </si>
+  <si>
+    <t>OpenMined/PyGrid-deprecated---see-PySyft-</t>
+  </si>
+  <si>
+    <t>probabl-ai/skore</t>
+  </si>
+  <si>
+    <t>benanne/kaggle-ndsb</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>2015-01-23T19:38:29Z</t>
+  </si>
+  <si>
+    <t>2019-04-18T10:29:56Z</t>
+  </si>
+  <si>
+    <t>2017-07-18T20:41:16Z</t>
+  </si>
+  <si>
+    <t>2015-10-30T19:19:57Z</t>
+  </si>
+  <si>
+    <t>2014-11-09T02:31:24Z</t>
+  </si>
+  <si>
+    <t>2023-09-19T06:19:22Z</t>
+  </si>
+  <si>
+    <t>2015-08-05T11:58:14Z</t>
+  </si>
+  <si>
+    <t>2015-10-06T15:26:08Z</t>
+  </si>
+  <si>
+    <t>2024-12-11T16:07:45Z</t>
+  </si>
+  <si>
+    <t>2025-10-11T11:19:21Z</t>
+  </si>
+  <si>
+    <t>2017-11-23T01:56:22Z</t>
+  </si>
+  <si>
+    <t>2014-02-23T18:55:40Z</t>
+  </si>
+  <si>
+    <t>2022-01-26T15:27:16Z</t>
+  </si>
+  <si>
+    <t>2015-02-23T14:18:06Z</t>
+  </si>
+  <si>
+    <t>2015-06-09T17:05:52Z</t>
+  </si>
+  <si>
+    <t>2020-10-15T02:27:45Z</t>
+  </si>
+  <si>
+    <t>2019-02-03T01:51:22Z</t>
+  </si>
+  <si>
+    <t>2018-02-07T09:36:04Z</t>
+  </si>
+  <si>
+    <t>2020-09-23T15:43:39Z</t>
+  </si>
+  <si>
+    <t>2022-04-03T14:40:53Z</t>
+  </si>
+  <si>
+    <t>2019-09-03T14:16:40Z</t>
+  </si>
+  <si>
+    <t>2011-11-20T07:23:02Z</t>
+  </si>
+  <si>
+    <t>2015-01-28T20:51:13Z</t>
+  </si>
+  <si>
+    <t>2022-10-17T05:46:43Z</t>
+  </si>
+  <si>
+    <t>2012-08-06T10:09:14Z</t>
+  </si>
+  <si>
+    <t>2015-09-25T08:37:27Z</t>
+  </si>
+  <si>
+    <t>2019-01-01T03:04:12Z</t>
+  </si>
+  <si>
+    <t>2018-01-26T20:53:03Z</t>
+  </si>
+  <si>
+    <t>2024-06-17T15:29:38Z</t>
+  </si>
+  <si>
+    <t>2015-03-25T17:04:56Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T22:44:46Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T09:40:07Z</t>
+  </si>
+  <si>
+    <t>2026-03-07T09:00:41Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T22:13:21Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T21:00:16Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T12:48:29Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T04:45:16Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T20:57:31Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T22:19:39Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T11:09:07Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T22:58:50Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T13:29:26Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T21:48:56Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T18:39:38Z</t>
+  </si>
+  <si>
+    <t>2026-02-09T10:17:58Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T01:01:57Z</t>
+  </si>
+  <si>
+    <t>2026-03-02T10:13:57Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T15:38:50Z</t>
+  </si>
+  <si>
+    <t>2026-03-07T05:32:35Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T07:49:06Z</t>
+  </si>
+  <si>
+    <t>2026-03-07T15:01:41Z</t>
+  </si>
+  <si>
+    <t>2026-02-03T09:24:03Z</t>
+  </si>
+  <si>
+    <t>2026-03-06T02:46:46Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T08:33:17Z</t>
+  </si>
+  <si>
+    <t>2026-03-05T09:46:24Z</t>
+  </si>
+  <si>
+    <t>2025-12-27T14:04:34Z</t>
+  </si>
+  <si>
+    <t>2025-12-28T02:39:56Z</t>
+  </si>
+  <si>
+    <t>2025-10-15T14:05:57Z</t>
+  </si>
+  <si>
+    <t>2026-03-07T15:12:54Z</t>
+  </si>
+  <si>
+    <t>2025-12-22T03:42:29Z</t>
+  </si>
+  <si>
+    <t>Exported at: 2026-03-09 02:49:58.452382</t>
+  </si>
+  <si>
+    <t>Significant-Gravitas/AutoGPT</t>
+  </si>
+  <si>
+    <t>yt-dlp/yt-dlp</t>
+  </si>
+  <si>
+    <t>Shubhamsaboo/awesome-llm-apps</t>
+  </si>
+  <si>
+    <t>anthropics/skills</t>
+  </si>
+  <si>
+    <t>infiniflow/ragflow</t>
+  </si>
+  <si>
+    <t>vllm-project/vllm</t>
+  </si>
+  <si>
+    <t>PaddlePaddle/PaddleOCR</t>
+  </si>
+  <si>
+    <t>OpenHands/OpenHands</t>
+  </si>
+  <si>
+    <t>labmlai/annotated_deep_learning_paper_implementations</t>
+  </si>
+  <si>
+    <t>openinterpreter/open-interpreter</t>
+  </si>
+  <si>
+    <t>unclecode/crawl4ai</t>
+  </si>
+  <si>
+    <t>CorentinJ/Real-Time-Voice-Cloning</t>
+  </si>
+  <si>
+    <t>pathwaycom/pathway</t>
+  </si>
+  <si>
+    <t>zylon-ai/private-gpt</t>
+  </si>
+  <si>
+    <t>ultralytics/yolov5</t>
+  </si>
+  <si>
+    <t>opendatalab/MinerU</t>
+  </si>
+  <si>
+    <t>Textualize/rich</t>
+  </si>
+  <si>
+    <t>RVC-Boss/GPT-SoVITS</t>
+  </si>
+  <si>
+    <t>Z4nzu/hackingtool</t>
+  </si>
+  <si>
+    <t>ultralytics/ultralytics</t>
+  </si>
+  <si>
+    <t>xai-org/grok-1</t>
+  </si>
+  <si>
+    <t>mem0ai/mem0</t>
+  </si>
+  <si>
+    <t>virattt/ai-hedge-fund</t>
+  </si>
+  <si>
+    <t>NanmiCoder/MediaCrawler</t>
+  </si>
+  <si>
+    <t>karpathy/nanochat</t>
+  </si>
+  <si>
+    <t>streamlit/streamlit</t>
+  </si>
+  <si>
+    <t>9001/copyparty</t>
+  </si>
+  <si>
+    <t>exo-explore/exo</t>
+  </si>
+  <si>
+    <t>zhayujie/chatgpt-on-wechat</t>
+  </si>
+  <si>
+    <t>hpcaitech/ColossalAI</t>
+  </si>
+  <si>
+    <t>2023-03-16T09:21:07Z</t>
+  </si>
+  <si>
+    <t>2020-10-26T04:22:55Z</t>
+  </si>
+  <si>
+    <t>2024-04-29T05:30:25Z</t>
+  </si>
+  <si>
+    <t>2025-09-22T15:53:31Z</t>
+  </si>
+  <si>
+    <t>2023-12-12T06:13:13Z</t>
+  </si>
+  <si>
+    <t>2023-02-09T11:23:20Z</t>
+  </si>
+  <si>
+    <t>2020-05-08T10:38:16Z</t>
+  </si>
+  <si>
+    <t>2024-03-13T03:33:31Z</t>
+  </si>
+  <si>
+    <t>2020-08-25T02:29:34Z</t>
+  </si>
+  <si>
+    <t>2023-07-14T07:10:44Z</t>
+  </si>
+  <si>
+    <t>2024-05-09T09:48:50Z</t>
+  </si>
+  <si>
+    <t>2019-05-26T08:56:15Z</t>
+  </si>
+  <si>
+    <t>2022-11-27T13:01:14Z</t>
+  </si>
+  <si>
+    <t>2023-05-02T09:15:31Z</t>
+  </si>
+  <si>
+    <t>2020-05-18T03:45:11Z</t>
+  </si>
+  <si>
+    <t>2024-02-29T08:52:34Z</t>
+  </si>
+  <si>
+    <t>2019-11-10T15:28:09Z</t>
+  </si>
+  <si>
+    <t>2024-01-14T18:05:21Z</t>
+  </si>
+  <si>
+    <t>2020-04-11T09:21:31Z</t>
+  </si>
+  <si>
+    <t>2022-09-11T16:39:45Z</t>
+  </si>
+  <si>
+    <t>2024-03-17T08:53:38Z</t>
+  </si>
+  <si>
+    <t>2023-06-20T08:58:36Z</t>
+  </si>
+  <si>
+    <t>2024-11-29T16:30:01Z</t>
+  </si>
+  <si>
+    <t>2023-06-09T12:14:34Z</t>
+  </si>
+  <si>
+    <t>2025-10-13T13:46:35Z</t>
+  </si>
+  <si>
+    <t>2019-08-24T00:14:52Z</t>
+  </si>
+  <si>
+    <t>2019-05-26T15:28:33Z</t>
+  </si>
+  <si>
+    <t>2024-06-24T18:36:22Z</t>
+  </si>
+  <si>
+    <t>2022-08-07T08:33:41Z</t>
+  </si>
+  <si>
+    <t>2021-10-28T16:19:44Z</t>
+  </si>
+  <si>
+    <t>Exported at: 2026-03-09 02:49:58.453429</t>
+  </si>
+  <si>
     <t>open_issues</t>
   </si>
   <si>
     <t>watchers</t>
   </si>
   <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>created_at</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
     <t>tensorflow/tensorflow</t>
   </si>
   <si>
@@ -58,9 +519,6 @@
     <t>C++</t>
   </si>
   <si>
-    <t>Python</t>
-  </si>
-  <si>
     <t>Scala</t>
   </si>
   <si>
@@ -79,22 +537,19 @@
     <t>2014-02-25T08:00:08Z</t>
   </si>
   <si>
-    <t>2026-03-05T22:34:46Z</t>
-  </si>
-  <si>
-    <t>2026-03-05T22:36:30Z</t>
-  </si>
-  <si>
-    <t>2026-03-05T21:44:37Z</t>
-  </si>
-  <si>
-    <t>2026-03-05T17:52:10Z</t>
-  </si>
-  <si>
-    <t>2026-03-05T21:23:08Z</t>
-  </si>
-  <si>
-    <t>Exported at: 2026-03-06 00:44:54.386230</t>
+    <t>2026-03-08T23:40:12Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:56:06Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:58:05Z</t>
+  </si>
+  <si>
+    <t>2026-03-08T23:56:12Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T00:40:37Z</t>
   </si>
 </sst>
 </file>
@@ -437,6 +892,1196 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="55.7109375" customWidth="1"/>
+    <col min="2" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="6" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>28909</v>
+      </c>
+      <c r="C2">
+        <v>8032</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>10782</v>
+      </c>
+      <c r="C3">
+        <v>1013</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>9858</v>
+      </c>
+      <c r="C4">
+        <v>2006</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>9712</v>
+      </c>
+      <c r="C5">
+        <v>2630</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9518</v>
+      </c>
+      <c r="C6">
+        <v>4722</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>8623</v>
+      </c>
+      <c r="C7">
+        <v>4385</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>6361</v>
+      </c>
+      <c r="C8">
+        <v>1769</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>5716</v>
+      </c>
+      <c r="C9">
+        <v>1536</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>5024</v>
+      </c>
+      <c r="C10">
+        <v>872</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>3769</v>
+      </c>
+      <c r="C11">
+        <v>544</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>3645</v>
+      </c>
+      <c r="C12">
+        <v>773</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>2525</v>
+      </c>
+      <c r="C13">
+        <v>283</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>2127</v>
+      </c>
+      <c r="C14">
+        <v>180</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>1749</v>
+      </c>
+      <c r="C15">
+        <v>1139</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>1547</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>1383</v>
+      </c>
+      <c r="C17">
+        <v>469</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>947</v>
+      </c>
+      <c r="C18">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>885</v>
+      </c>
+      <c r="C19">
+        <v>529</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>864</v>
+      </c>
+      <c r="C20">
+        <v>433</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>784</v>
+      </c>
+      <c r="C21">
+        <v>216</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>775</v>
+      </c>
+      <c r="C22">
+        <v>144</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>762</v>
+      </c>
+      <c r="C23">
+        <v>265</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>750</v>
+      </c>
+      <c r="C24">
+        <v>167</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25">
+        <v>728</v>
+      </c>
+      <c r="C25">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>707</v>
+      </c>
+      <c r="C26">
+        <v>301</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>692</v>
+      </c>
+      <c r="C27">
+        <v>271</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>616</v>
+      </c>
+      <c r="C28">
+        <v>44</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>616</v>
+      </c>
+      <c r="C29">
+        <v>215</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>594</v>
+      </c>
+      <c r="C30">
+        <v>127</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>566</v>
+      </c>
+      <c r="C31">
+        <v>198</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="55.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2">
+        <v>182272</v>
+      </c>
+      <c r="C2">
+        <v>46201</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3">
+        <v>150199</v>
+      </c>
+      <c r="C3">
+        <v>12176</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>100907</v>
+      </c>
+      <c r="C4">
+        <v>14666</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5">
+        <v>87266</v>
+      </c>
+      <c r="C5">
+        <v>9258</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6">
+        <v>74431</v>
+      </c>
+      <c r="C6">
+        <v>8303</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7">
+        <v>72446</v>
+      </c>
+      <c r="C7">
+        <v>14104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8">
+        <v>71832</v>
+      </c>
+      <c r="C8">
+        <v>9922</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9">
+        <v>68767</v>
+      </c>
+      <c r="C9">
+        <v>8596</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10">
+        <v>65874</v>
+      </c>
+      <c r="C10">
+        <v>6618</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11">
+        <v>62589</v>
+      </c>
+      <c r="C11">
+        <v>5389</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12">
+        <v>61548</v>
+      </c>
+      <c r="C12">
+        <v>6287</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13">
+        <v>59508</v>
+      </c>
+      <c r="C13">
+        <v>9422</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14">
+        <v>59463</v>
+      </c>
+      <c r="C14">
+        <v>1610</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15">
+        <v>57157</v>
+      </c>
+      <c r="C15">
+        <v>7607</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16">
+        <v>56940</v>
+      </c>
+      <c r="C16">
+        <v>17426</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17">
+        <v>55720</v>
+      </c>
+      <c r="C17">
+        <v>4618</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18">
+        <v>55713</v>
+      </c>
+      <c r="C18">
+        <v>2059</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19">
+        <v>55594</v>
+      </c>
+      <c r="C19">
+        <v>6075</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20">
+        <v>55193</v>
+      </c>
+      <c r="C20">
+        <v>6012</v>
+      </c>
+      <c r="D20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21">
+        <v>54073</v>
+      </c>
+      <c r="C21">
+        <v>10398</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22">
+        <v>51535</v>
+      </c>
+      <c r="C22">
+        <v>8484</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23">
+        <v>49066</v>
+      </c>
+      <c r="C23">
+        <v>5472</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24">
+        <v>46822</v>
+      </c>
+      <c r="C24">
+        <v>8147</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25">
+        <v>45039</v>
+      </c>
+      <c r="C25">
+        <v>9800</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B26">
+        <v>45010</v>
+      </c>
+      <c r="C26">
+        <v>5967</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27">
+        <v>43803</v>
+      </c>
+      <c r="C27">
+        <v>4121</v>
+      </c>
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28">
+        <v>43016</v>
+      </c>
+      <c r="C28">
+        <v>1756</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29">
+        <v>42316</v>
+      </c>
+      <c r="C29">
+        <v>2903</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B30">
+        <v>42011</v>
+      </c>
+      <c r="C30">
+        <v>9801</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31">
+        <v>41360</v>
+      </c>
+      <c r="C31">
+        <v>4527</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -459,154 +2104,154 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>161</v>
       </c>
       <c r="B2">
-        <v>194010</v>
+        <v>194046</v>
       </c>
       <c r="C2">
-        <v>75217</v>
+        <v>75222</v>
       </c>
       <c r="D2">
-        <v>3599</v>
+        <v>3712</v>
       </c>
       <c r="E2">
-        <v>194010</v>
+        <v>194046</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="B3">
-        <v>97984</v>
+        <v>98054</v>
       </c>
       <c r="C3">
-        <v>27081</v>
+        <v>27115</v>
       </c>
       <c r="D3">
-        <v>18086</v>
+        <v>18072</v>
       </c>
       <c r="E3">
-        <v>97984</v>
+        <v>98054</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="B4">
-        <v>65297</v>
+        <v>65337</v>
       </c>
       <c r="C4">
         <v>26751</v>
       </c>
       <c r="D4">
-        <v>2136</v>
+        <v>2140</v>
       </c>
       <c r="E4">
-        <v>65297</v>
+        <v>65337</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
       <c r="B5">
         <v>63911</v>
       </c>
       <c r="C5">
-        <v>19714</v>
+        <v>19712</v>
       </c>
       <c r="D5">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E5">
         <v>63911</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B6">
-        <v>42931</v>
+        <v>42947</v>
       </c>
       <c r="C6">
-        <v>29089</v>
+        <v>29086</v>
       </c>
       <c r="D6">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="E6">
-        <v>42931</v>
+        <v>42947</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
